--- a/publication_outputs/publication_tables.xlsx
+++ b/publication_outputs/publication_tables.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t xml:space="preserve">Step</t>
   </si>
@@ -41,13 +41,10 @@
     <t xml:space="preserve">Questionnaires with all fields answered</t>
   </si>
   <si>
-    <t xml:space="preserve">Complete questionnaires used as the starting sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">– full-time students not employed in a statistics-related position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">– none of the inclusion criteria met (employment status missing)</t>
+    <t xml:space="preserve">– retired / unemployed / full-time students (or other / missing status)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">– not working, or working outside Switzerland</t>
   </si>
   <si>
     <t xml:space="preserve">Eligible respondents (analysis sample)</t>
@@ -92,40 +89,43 @@
     <t xml:space="preserve">No management</t>
   </si>
   <si>
+    <t xml:space="preserve">120 089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≥ 200 000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor of applied science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University bachelor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master of applied science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University master</t>
+  </si>
+  <si>
     <t xml:space="preserve">118 750</t>
   </si>
   <si>
-    <t xml:space="preserve">Top management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≥ 200 000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highest degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor of applied science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University bachelor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master of applied science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160 000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University master</t>
-  </si>
-  <si>
     <t xml:space="preserve">PhD</t>
   </si>
   <si>
-    <t xml:space="preserve">135 147</t>
+    <t xml:space="preserve">135 000</t>
   </si>
   <si>
     <t xml:space="preserve">Other</t>
@@ -146,15 +146,12 @@
     <t xml:space="preserve">Espace Mittelland (BE, FR, SO, NE, JU)</t>
   </si>
   <si>
-    <t xml:space="preserve">135 294</t>
+    <t xml:space="preserve">137 092</t>
   </si>
   <si>
     <t xml:space="preserve">Lake Geneva region (VD, VS, GE)</t>
   </si>
   <si>
-    <t xml:space="preserve">120 089</t>
-  </si>
-  <si>
     <t xml:space="preserve">Northwestern Switzerland (BS, BL, AG)</t>
   </si>
   <si>
@@ -188,7 +185,7 @@
     <t xml:space="preserve">112 500 (16)</t>
   </si>
   <si>
-    <t xml:space="preserve">121 429 (29)</t>
+    <t xml:space="preserve">120 089 (28)</t>
   </si>
   <si>
     <t xml:space="preserve">145 000 (16)</t>
@@ -215,15 +212,9 @@
     <t xml:space="preserve">112 500</t>
   </si>
   <si>
-    <t xml:space="preserve">121 429</t>
-  </si>
-  <si>
     <t xml:space="preserve">115 000</t>
   </si>
   <si>
-    <t xml:space="preserve">135 000</t>
-  </si>
-  <si>
     <t xml:space="preserve">Block</t>
   </si>
   <si>
@@ -248,7 +239,7 @@
     <t xml:space="preserve">115 000 (13)</t>
   </si>
   <si>
-    <t xml:space="preserve">155 000 (19)</t>
+    <t xml:space="preserve">155 000 (17)</t>
   </si>
   <si>
     <t xml:space="preserve">Public administration</t>
@@ -284,19 +275,19 @@
     <t xml:space="preserve">135 000 (14)</t>
   </si>
   <si>
-    <t xml:space="preserve">150 000 (19)</t>
+    <t xml:space="preserve">152 500 (18)</t>
   </si>
   <si>
     <t xml:space="preserve">Doctorate (PhD)</t>
   </si>
   <si>
-    <t xml:space="preserve">100 625 (14)</t>
+    <t xml:space="preserve">106 250 (13)</t>
   </si>
   <si>
     <t xml:space="preserve">135 000 (32)</t>
   </si>
   <si>
-    <t xml:space="preserve">156 250 (28)</t>
+    <t xml:space="preserve">156 250 (26)</t>
   </si>
   <si>
     <t xml:space="preserve">Career stage</t>
@@ -326,7 +317,7 @@
     <t xml:space="preserve">143 333</t>
   </si>
   <si>
-    <t xml:space="preserve">100 625</t>
+    <t xml:space="preserve">106 250</t>
   </si>
   <si>
     <t xml:space="preserve">156 250</t>
@@ -335,16 +326,16 @@
     <t xml:space="preserve">95 000</t>
   </si>
   <si>
-    <t xml:space="preserve">150 000</t>
+    <t xml:space="preserve">152 500</t>
   </si>
   <si>
     <t xml:space="preserve">Difference</t>
   </si>
   <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
   </si>
   <si>
     <t xml:space="preserve">Median years of experience</t>
@@ -353,46 +344,46 @@
     <t xml:space="preserve">10</t>
   </si>
   <si>
-    <t xml:space="preserve">15</t>
+    <t xml:space="preserve">14</t>
   </si>
   <si>
     <t xml:space="preserve">In a management position (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3</t>
+    <t xml:space="preserve">39.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2</t>
   </si>
   <si>
     <t xml:space="preserve">PhD (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0</t>
+    <t xml:space="preserve">61.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2</t>
   </si>
   <si>
     <t xml:space="preserve">Working part-time (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3</t>
+    <t xml:space="preserve">48.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6</t>
   </si>
   <si>
     <t xml:space="preserve">Median FTE salary, all (CHF)</t>
   </si>
   <si>
-    <t xml:space="preserve">−18%</t>
+    <t xml:space="preserve">−17%</t>
   </si>
   <si>
     <t xml:space="preserve">   0–5 years of experience</t>
   </si>
   <si>
-    <t xml:space="preserve">95 000 (23)</t>
+    <t xml:space="preserve">95 000 (22)</t>
   </si>
   <si>
     <t xml:space="preserve">106 250 (17)</t>
@@ -419,7 +410,7 @@
     <t xml:space="preserve">141 667 (17)</t>
   </si>
   <si>
-    <t xml:space="preserve">155 625 (32)</t>
+    <t xml:space="preserve">156 250 (29)</t>
   </si>
   <si>
     <t xml:space="preserve">Median experience (years)</t>
@@ -1087,7 +1078,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="68.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="73.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="3.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1120,7 +1111,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>142</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1128,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1136,7 +1127,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
@@ -1144,19 +1135,11 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -1176,58 +1159,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B2" s="26" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="28" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="E2" s="29" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B3" s="26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="27" t="n">
         <v>34</v>
       </c>
       <c r="D3" s="28" t="n">
-        <v>55.6</v>
+        <v>56.5</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>56.7</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B4" s="26" t="n">
         <v>7</v>
@@ -1236,44 +1219,44 @@
         <v>8</v>
       </c>
       <c r="D4" s="28" t="n">
-        <v>9.7</v>
+        <v>10.1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B5" s="26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>11</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>15.3</v>
+        <v>14.5</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>16.7</v>
+        <v>15.9</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1302,51 +1285,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B2" s="30" t="n">
         <v>17</v>
       </c>
       <c r="C2" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="32" t="n">
         <v>95000</v>
       </c>
       <c r="E2" s="33" t="n">
-        <v>80000</v>
+        <v>87188</v>
       </c>
       <c r="F2" s="34" t="n">
         <v>106250</v>
@@ -1358,7 +1341,7 @@
         <v>125000</v>
       </c>
       <c r="I2" s="37" t="n">
-        <v>116875</v>
+        <v>117812</v>
       </c>
       <c r="J2" s="38" t="n">
         <v>-10.6</v>
@@ -1366,7 +1349,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B3" s="30" t="n">
         <v>26</v>
@@ -1398,10 +1381,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" s="30" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="31" t="n">
         <v>17</v>
@@ -1413,7 +1396,7 @@
         <v>118750</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>155625</v>
+        <v>156250</v>
       </c>
       <c r="G4" s="35" t="n">
         <v>141667</v>
@@ -1425,7 +1408,7 @@
         <v>205000</v>
       </c>
       <c r="J4" s="38" t="n">
-        <v>-9</v>
+        <v>-9.3</v>
       </c>
     </row>
   </sheetData>
@@ -1453,42 +1436,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="40" t="n">
         <v>33</v>
@@ -1500,59 +1483,59 @@
         <v>105000</v>
       </c>
       <c r="F2" s="43" t="n">
-        <v>127778</v>
+        <v>129514</v>
       </c>
       <c r="G2" s="44" t="n">
         <v>118750</v>
       </c>
       <c r="H2" s="45" t="n">
-        <v>147500</v>
+        <v>148750</v>
       </c>
       <c r="I2" s="46" t="n">
         <v>145000</v>
       </c>
       <c r="J2" s="47" t="n">
-        <v>-7.1</v>
+        <v>-8.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="39" t="n">
         <v>17</v>
-      </c>
-      <c r="B3" s="39" t="n">
-        <v>18</v>
       </c>
       <c r="C3" s="40" t="n">
         <v>19</v>
       </c>
       <c r="D3" s="41" t="n">
-        <v>140417</v>
+        <v>138889</v>
       </c>
       <c r="E3" s="42" t="n">
         <v>110871</v>
       </c>
       <c r="F3" s="43" t="n">
-        <v>152500</v>
+        <v>155000</v>
       </c>
       <c r="G3" s="44" t="n">
         <v>125000</v>
       </c>
       <c r="H3" s="45" t="n">
-        <v>192500</v>
+        <v>195000</v>
       </c>
       <c r="I3" s="46" t="n">
         <v>162500</v>
       </c>
       <c r="J3" s="47" t="n">
-        <v>-18</v>
+        <v>-19.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="40" t="n">
         <v>4</v>
@@ -1605,39 +1588,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C2" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>118750</v>
@@ -1649,47 +1632,47 @@
         <v>185000</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>105000</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>118750</v>
+        <v>120089</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>145000</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>205000</v>
@@ -1701,18 +1684,18 @@
         <v>205000</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2</v>
@@ -1721,18 +1704,18 @@
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
       <c r="G5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
@@ -1741,18 +1724,18 @@
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>12</v>
@@ -1767,24 +1750,24 @@
         <v>190000</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>100000</v>
+        <v>97500</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>118750</v>
@@ -1793,41 +1776,41 @@
         <v>145000</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>106373</v>
+        <v>106496</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>135147</v>
+        <v>135000</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>182500</v>
+        <v>180000</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>33</v>
@@ -1839,10 +1822,10 @@
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
       <c r="G10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1853,22 +1836,22 @@
         <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>110625</v>
+        <v>106250</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>145000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>180000</v>
+        <v>177500</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -1879,22 +1862,22 @@
         <v>36</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>95000</v>
+        <v>102500</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>118750</v>
+        <v>120089</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>145000</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -1905,13 +1888,13 @@
         <v>38</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>115000</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>135294</v>
+        <v>137092</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>156250</v>
@@ -1920,7 +1903,7 @@
         <v>39</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -1931,22 +1914,22 @@
         <v>40</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>105000</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>120089</v>
+        <v>118750</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>148750</v>
+        <v>145000</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -1954,7 +1937,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>24</v>
@@ -1969,10 +1952,10 @@
         <v>187188</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -1980,7 +1963,7 @@
         <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>8</v>
@@ -1989,10 +1972,10 @@
       <c r="E16" s="6"/>
       <c r="F16" s="7"/>
       <c r="G16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -2000,7 +1983,7 @@
         <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>30</v>
@@ -2015,10 +1998,10 @@
         <v>155000</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2042,19 +2025,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -2062,16 +2045,16 @@
         <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -2079,67 +2062,67 @@
         <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2166,28 +2149,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
@@ -2195,7 +2178,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="8" t="n">
         <v>17</v>
@@ -2210,10 +2193,10 @@
         <v>150000</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -2221,7 +2204,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="8" t="n">
         <v>15</v>
@@ -2236,10 +2219,10 @@
         <v>160000</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -2247,7 +2230,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>5</v>
@@ -2256,10 +2239,10 @@
       <c r="E4" s="10"/>
       <c r="F4" s="11"/>
       <c r="G4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -2267,7 +2250,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>37</v>
@@ -2282,10 +2265,10 @@
         <v>165000</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -2293,7 +2276,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>16</v>
@@ -2308,10 +2291,10 @@
         <v>133854</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -2319,7 +2302,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>6</v>
@@ -2328,10 +2311,10 @@
       <c r="E7" s="10"/>
       <c r="F7" s="11"/>
       <c r="G7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -2339,19 +2322,19 @@
         <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
       <c r="G8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -2359,33 +2342,33 @@
         <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>105000</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>121429</v>
+        <v>120089</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>150000</v>
+        <v>146250</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>16</v>
@@ -2400,18 +2383,18 @@
         <v>167500</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>7</v>
@@ -2420,18 +2403,18 @@
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
       <c r="G11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>1</v>
@@ -2440,18 +2423,18 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>24</v>
@@ -2466,18 +2449,18 @@
         <v>187188</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>6</v>
@@ -2486,18 +2469,18 @@
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
       <c r="G14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>1</v>
@@ -2506,18 +2489,18 @@
       <c r="E15" s="10"/>
       <c r="F15" s="11"/>
       <c r="G15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>1</v>
@@ -2526,18 +2509,18 @@
       <c r="E16" s="10"/>
       <c r="F16" s="11"/>
       <c r="G16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>8</v>
@@ -2546,18 +2529,18 @@
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
       <c r="G17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>17</v>
@@ -2572,18 +2555,18 @@
         <v>145000</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>7</v>
@@ -2592,18 +2575,18 @@
       <c r="E19" s="10"/>
       <c r="F19" s="11"/>
       <c r="G19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>2</v>
@@ -2612,18 +2595,18 @@
       <c r="E20" s="10"/>
       <c r="F20" s="11"/>
       <c r="G20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>26</v>
@@ -2638,10 +2621,10 @@
         <v>184062</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2665,121 +2648,121 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2806,36 +2789,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>11</v>
@@ -2850,18 +2833,18 @@
         <v>95000</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>13</v>
@@ -2876,21 +2859,21 @@
         <v>156250</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>135000</v>
@@ -2902,18 +2885,18 @@
         <v>205000</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>14</v>
@@ -2928,18 +2911,18 @@
         <v>127083</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>8</v>
@@ -2948,18 +2931,18 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>9</v>
@@ -2968,38 +2951,38 @@
       <c r="E7" s="14"/>
       <c r="F7" s="15"/>
       <c r="G7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="14"/>
       <c r="F8" s="15"/>
       <c r="G8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>13</v>
@@ -3014,38 +2997,38 @@
         <v>185000</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="14"/>
       <c r="F10" s="15"/>
       <c r="G10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10</v>
@@ -3060,18 +3043,18 @@
         <v>118750</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>13</v>
@@ -3086,18 +3069,18 @@
         <v>150000</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>14</v>
@@ -3112,10 +3095,10 @@
         <v>154688</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3142,62 +3125,62 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="17" t="n">
         <v>95000</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>100625</v>
+        <v>106250</v>
       </c>
       <c r="F2" s="19" t="n">
         <v>118750</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>32</v>
@@ -3212,21 +3195,21 @@
         <v>177500</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="17" t="n">
         <v>135000</v>
@@ -3238,18 +3221,18 @@
         <v>205000</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>26</v>
@@ -3264,18 +3247,18 @@
         <v>115000</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>14</v>
@@ -3290,36 +3273,36 @@
         <v>154688</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>143333</v>
+        <v>145000</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>150000</v>
+        <v>152500</v>
       </c>
       <c r="F7" s="19" t="n">
         <v>195000</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3342,7 +3325,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -3351,7 +3334,7 @@
         <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
@@ -3359,125 +3342,125 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3510,22 +3493,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2">
@@ -3533,25 +3516,25 @@
         <v>35</v>
       </c>
       <c r="B2" s="20" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" s="21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="22" t="n">
-        <v>42.3</v>
+        <v>41.2</v>
       </c>
       <c r="E2" s="23" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
       <c r="F2" s="24" t="n">
-        <v>29.3</v>
+        <v>30.6</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>145000</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3559,25 +3542,25 @@
         <v>36</v>
       </c>
       <c r="B3" s="20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="21" t="n">
         <v>10</v>
       </c>
       <c r="D3" s="22" t="n">
-        <v>39</v>
+        <v>39.7</v>
       </c>
       <c r="E3" s="23" t="n">
-        <v>62.3</v>
+        <v>61.7</v>
       </c>
       <c r="F3" s="24" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>118750</v>
+        <v>120089</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
